--- a/SACCO_Master_Performance_Report.xlsx
+++ b/SACCO_Master_Performance_Report.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,7 +429,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Total Active Loan Book</v>
+        <v>Total Active Loan Principal</v>
       </c>
       <c r="B4" t="str">
         <v>UGX 8,302,000</v>
@@ -451,17 +451,9 @@
         <v>UGX 1,444,500</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Total SACCO Interest Earned</v>
-      </c>
-      <c r="B7" t="str">
-        <v>UGX 5,771,700</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1046,7 +1038,7 @@
         <v>Date</v>
       </c>
       <c r="B1" t="str">
-        <v>Member_ID</v>
+        <v>Member</v>
       </c>
       <c r="C1" t="str">
         <v>Amount_UGX</v>
@@ -1059,8 +1051,8 @@
       <c r="A2" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B2">
-        <v>2</v>
+      <c r="B2" t="str">
+        <v>Ariho Micheal</v>
       </c>
       <c r="C2">
         <v>50000</v>
@@ -1073,8 +1065,8 @@
       <c r="A3" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B3">
-        <v>3</v>
+      <c r="B3" t="str">
+        <v>Kyarisiima Justus</v>
       </c>
       <c r="C3">
         <v>100000</v>
@@ -1087,8 +1079,8 @@
       <c r="A4" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B4">
-        <v>4</v>
+      <c r="B4" t="str">
+        <v>Kasumbuza Cosmas</v>
       </c>
       <c r="C4">
         <v>100000</v>
@@ -1101,8 +1093,8 @@
       <c r="A5" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B5">
-        <v>5</v>
+      <c r="B5" t="str">
+        <v>Nayebare Prossy</v>
       </c>
       <c r="C5">
         <v>50000</v>
@@ -1115,8 +1107,8 @@
       <c r="A6" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B6">
-        <v>6</v>
+      <c r="B6" t="str">
+        <v>Sonia</v>
       </c>
       <c r="C6">
         <v>50000</v>
@@ -1129,8 +1121,8 @@
       <c r="A7" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B7">
-        <v>7</v>
+      <c r="B7" t="str">
+        <v>Kazoora Francis</v>
       </c>
       <c r="C7">
         <v>50000</v>
@@ -1143,8 +1135,8 @@
       <c r="A8" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B8">
-        <v>8</v>
+      <c r="B8" t="str">
+        <v>Mucunguzi Junior</v>
       </c>
       <c r="C8">
         <v>75000</v>
@@ -1157,8 +1149,8 @@
       <c r="A9" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B9">
-        <v>9</v>
+      <c r="B9" t="str">
+        <v>Ainembabazi Queen</v>
       </c>
       <c r="C9">
         <v>50000</v>
@@ -1171,8 +1163,8 @@
       <c r="A10" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B10">
-        <v>10</v>
+      <c r="B10" t="str">
+        <v>Kanyesigye immaculate</v>
       </c>
       <c r="C10">
         <v>50000</v>
@@ -1185,8 +1177,8 @@
       <c r="A11" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B11">
-        <v>11</v>
+      <c r="B11" t="str">
+        <v>Ainebyona Mebo</v>
       </c>
       <c r="C11">
         <v>150000</v>
@@ -1199,8 +1191,8 @@
       <c r="A12" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B12">
-        <v>12</v>
+      <c r="B12" t="str">
+        <v>Mzee Fred Kakombe</v>
       </c>
       <c r="C12">
         <v>50000</v>
@@ -1213,8 +1205,8 @@
       <c r="A13" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B13">
-        <v>13</v>
+      <c r="B13" t="str">
+        <v>Jesica Kamuseveni</v>
       </c>
       <c r="C13">
         <v>50000</v>
@@ -1227,8 +1219,8 @@
       <c r="A14" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B14">
-        <v>14</v>
+      <c r="B14" t="str">
+        <v>Mathias Twijukye</v>
       </c>
       <c r="C14">
         <v>50000</v>
@@ -1241,8 +1233,8 @@
       <c r="A15" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B15">
-        <v>15</v>
+      <c r="B15" t="str">
+        <v>Nyangoma Sharon</v>
       </c>
       <c r="C15">
         <v>200000</v>
@@ -1255,8 +1247,8 @@
       <c r="A16" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B16">
-        <v>16</v>
+      <c r="B16" t="str">
+        <v>Rwihura Duncan</v>
       </c>
       <c r="C16">
         <v>75000</v>
@@ -1269,8 +1261,8 @@
       <c r="A17" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B17">
-        <v>17</v>
+      <c r="B17" t="str">
+        <v>Nasasira Ainaea</v>
       </c>
       <c r="C17">
         <v>150000</v>
@@ -1283,8 +1275,8 @@
       <c r="A18" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B18">
-        <v>18</v>
+      <c r="B18" t="str">
+        <v>Nimusiima Sharon</v>
       </c>
       <c r="C18">
         <v>50000</v>
@@ -1297,8 +1289,8 @@
       <c r="A19" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B19">
-        <v>19</v>
+      <c r="B19" t="str">
+        <v>Mathias Akampurira</v>
       </c>
       <c r="C19">
         <v>175000</v>
@@ -1311,8 +1303,8 @@
       <c r="A20" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B20">
-        <v>20</v>
+      <c r="B20" t="str">
+        <v>Fednand Tumusiime</v>
       </c>
       <c r="C20">
         <v>50000</v>
@@ -1325,8 +1317,8 @@
       <c r="A21" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B21">
-        <v>21</v>
+      <c r="B21" t="str">
+        <v>Simon Kulooba</v>
       </c>
       <c r="C21">
         <v>50000</v>
@@ -1339,8 +1331,8 @@
       <c r="A22" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B22">
-        <v>22</v>
+      <c r="B22" t="str">
+        <v>Frank Begumanya</v>
       </c>
       <c r="C22">
         <v>50000</v>
@@ -1353,8 +1345,8 @@
       <c r="A23" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B23">
-        <v>23</v>
+      <c r="B23" t="str">
+        <v>Alex Muzahura</v>
       </c>
       <c r="C23">
         <v>150000</v>
@@ -1367,8 +1359,8 @@
       <c r="A24" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B24">
-        <v>24</v>
+      <c r="B24" t="str">
+        <v>kyomugasho jolly</v>
       </c>
       <c r="C24">
         <v>300000</v>
@@ -1381,8 +1373,8 @@
       <c r="A25" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B25">
-        <v>25</v>
+      <c r="B25" t="str">
+        <v>Madam director</v>
       </c>
       <c r="C25">
         <v>2000000</v>
@@ -1395,8 +1387,8 @@
       <c r="A26" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B26">
-        <v>2</v>
+      <c r="B26" t="str">
+        <v>Ariho Micheal</v>
       </c>
       <c r="C26">
         <v>50000</v>
@@ -1409,8 +1401,8 @@
       <c r="A27" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B27">
-        <v>3</v>
+      <c r="B27" t="str">
+        <v>Kyarisiima Justus</v>
       </c>
       <c r="C27">
         <v>100000</v>
@@ -1423,8 +1415,8 @@
       <c r="A28" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B28">
-        <v>4</v>
+      <c r="B28" t="str">
+        <v>Kasumbuza Cosmas</v>
       </c>
       <c r="C28">
         <v>100000</v>
@@ -1437,8 +1429,8 @@
       <c r="A29" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B29">
-        <v>5</v>
+      <c r="B29" t="str">
+        <v>Nayebare Prossy</v>
       </c>
       <c r="C29">
         <v>50000</v>
@@ -1451,8 +1443,8 @@
       <c r="A30" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B30">
-        <v>6</v>
+      <c r="B30" t="str">
+        <v>Sonia</v>
       </c>
       <c r="C30">
         <v>50000</v>
@@ -1465,8 +1457,8 @@
       <c r="A31" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B31">
-        <v>7</v>
+      <c r="B31" t="str">
+        <v>Kazoora Francis</v>
       </c>
       <c r="C31">
         <v>50000</v>
@@ -1479,8 +1471,8 @@
       <c r="A32" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B32">
-        <v>8</v>
+      <c r="B32" t="str">
+        <v>Mucunguzi Junior</v>
       </c>
       <c r="C32">
         <v>75000</v>
@@ -1493,8 +1485,8 @@
       <c r="A33" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B33">
-        <v>9</v>
+      <c r="B33" t="str">
+        <v>Ainembabazi Queen</v>
       </c>
       <c r="C33">
         <v>150000</v>
@@ -1507,8 +1499,8 @@
       <c r="A34" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B34">
-        <v>10</v>
+      <c r="B34" t="str">
+        <v>Kanyesigye immaculate</v>
       </c>
       <c r="C34">
         <v>50000</v>
@@ -1521,8 +1513,8 @@
       <c r="A35" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B35">
-        <v>11</v>
+      <c r="B35" t="str">
+        <v>Ainebyona Mebo</v>
       </c>
       <c r="C35">
         <v>150000</v>
@@ -1535,8 +1527,8 @@
       <c r="A36" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B36">
-        <v>12</v>
+      <c r="B36" t="str">
+        <v>Mzee Fred Kakombe</v>
       </c>
       <c r="C36">
         <v>50000</v>
@@ -1549,8 +1541,8 @@
       <c r="A37" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B37">
-        <v>13</v>
+      <c r="B37" t="str">
+        <v>Jesica Kamuseveni</v>
       </c>
       <c r="C37">
         <v>50000</v>
@@ -1563,8 +1555,8 @@
       <c r="A38" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B38">
-        <v>14</v>
+      <c r="B38" t="str">
+        <v>Mathias Twijukye</v>
       </c>
       <c r="C38">
         <v>50000</v>
@@ -1577,8 +1569,8 @@
       <c r="A39" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B39">
-        <v>15</v>
+      <c r="B39" t="str">
+        <v>Nyangoma Sharon</v>
       </c>
       <c r="C39">
         <v>200000</v>
@@ -1591,8 +1583,8 @@
       <c r="A40" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B40">
-        <v>16</v>
+      <c r="B40" t="str">
+        <v>Rwihura Duncan</v>
       </c>
       <c r="C40">
         <v>75000</v>
@@ -1605,8 +1597,8 @@
       <c r="A41" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B41">
-        <v>17</v>
+      <c r="B41" t="str">
+        <v>Nasasira Ainaea</v>
       </c>
       <c r="C41">
         <v>50000</v>
@@ -1619,8 +1611,8 @@
       <c r="A42" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B42">
-        <v>18</v>
+      <c r="B42" t="str">
+        <v>Nimusiima Sharon</v>
       </c>
       <c r="C42">
         <v>50000</v>
@@ -1633,8 +1625,8 @@
       <c r="A43" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B43">
-        <v>19</v>
+      <c r="B43" t="str">
+        <v>Mathias Akampurira</v>
       </c>
       <c r="C43">
         <v>175000</v>
@@ -1647,8 +1639,8 @@
       <c r="A44" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B44">
-        <v>20</v>
+      <c r="B44" t="str">
+        <v>Fednand Tumusiime</v>
       </c>
       <c r="C44">
         <v>75000</v>
@@ -1661,8 +1653,8 @@
       <c r="A45" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B45">
-        <v>21</v>
+      <c r="B45" t="str">
+        <v>Simon Kulooba</v>
       </c>
       <c r="C45">
         <v>50000</v>
@@ -1675,8 +1667,8 @@
       <c r="A46" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B46">
-        <v>22</v>
+      <c r="B46" t="str">
+        <v>Frank Begumanya</v>
       </c>
       <c r="C46">
         <v>50000</v>
@@ -1689,8 +1681,8 @@
       <c r="A47" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B47">
-        <v>31</v>
+      <c r="B47" t="str">
+        <v>muzahura  alex</v>
       </c>
       <c r="C47">
         <v>150000</v>
@@ -1703,8 +1695,8 @@
       <c r="A48" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B48">
-        <v>24</v>
+      <c r="B48" t="str">
+        <v>kyomugasho jolly</v>
       </c>
       <c r="C48">
         <v>300000</v>
@@ -1717,8 +1709,8 @@
       <c r="A49" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B49">
-        <v>25</v>
+      <c r="B49" t="str">
+        <v>Madam director</v>
       </c>
       <c r="C49">
         <v>2000000</v>
@@ -1731,8 +1723,8 @@
       <c r="A50" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B50">
-        <v>2</v>
+      <c r="B50" t="str">
+        <v>Ariho Micheal</v>
       </c>
       <c r="C50">
         <v>50000</v>
@@ -1745,8 +1737,8 @@
       <c r="A51" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B51">
-        <v>3</v>
+      <c r="B51" t="str">
+        <v>Kyarisiima Justus</v>
       </c>
       <c r="C51">
         <v>100000</v>
@@ -1759,8 +1751,8 @@
       <c r="A52" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B52">
-        <v>4</v>
+      <c r="B52" t="str">
+        <v>Kasumbuza Cosmas</v>
       </c>
       <c r="C52">
         <v>100000</v>
@@ -1773,8 +1765,8 @@
       <c r="A53" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B53">
-        <v>5</v>
+      <c r="B53" t="str">
+        <v>Nayebare Prossy</v>
       </c>
       <c r="C53">
         <v>50000</v>
@@ -1787,8 +1779,8 @@
       <c r="A54" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B54">
-        <v>6</v>
+      <c r="B54" t="str">
+        <v>Sonia</v>
       </c>
       <c r="C54">
         <v>50000</v>
@@ -1801,8 +1793,8 @@
       <c r="A55" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B55">
-        <v>8</v>
+      <c r="B55" t="str">
+        <v>Mucunguzi Junior</v>
       </c>
       <c r="C55">
         <v>75000</v>
@@ -1815,8 +1807,8 @@
       <c r="A56" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B56">
-        <v>9</v>
+      <c r="B56" t="str">
+        <v>Ainembabazi Queen</v>
       </c>
       <c r="C56">
         <v>150000</v>
@@ -1829,8 +1821,8 @@
       <c r="A57" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B57">
-        <v>11</v>
+      <c r="B57" t="str">
+        <v>Ainebyona Mebo</v>
       </c>
       <c r="C57">
         <v>150000</v>
@@ -1843,8 +1835,8 @@
       <c r="A58" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B58">
-        <v>12</v>
+      <c r="B58" t="str">
+        <v>Mzee Fred Kakombe</v>
       </c>
       <c r="C58">
         <v>50000</v>
@@ -1857,8 +1849,8 @@
       <c r="A59" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B59">
-        <v>13</v>
+      <c r="B59" t="str">
+        <v>Jesica Kamuseveni</v>
       </c>
       <c r="C59">
         <v>50000</v>
@@ -1871,8 +1863,8 @@
       <c r="A60" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B60">
-        <v>14</v>
+      <c r="B60" t="str">
+        <v>Mathias Twijukye</v>
       </c>
       <c r="C60">
         <v>50000</v>
@@ -1885,8 +1877,8 @@
       <c r="A61" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B61">
-        <v>15</v>
+      <c r="B61" t="str">
+        <v>Nyangoma Sharon</v>
       </c>
       <c r="C61">
         <v>200000</v>
@@ -1899,8 +1891,8 @@
       <c r="A62" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B62">
-        <v>17</v>
+      <c r="B62" t="str">
+        <v>Nasasira Ainaea</v>
       </c>
       <c r="C62">
         <v>50000</v>
@@ -1913,8 +1905,8 @@
       <c r="A63" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B63">
-        <v>18</v>
+      <c r="B63" t="str">
+        <v>Nimusiima Sharon</v>
       </c>
       <c r="C63">
         <v>50000</v>
@@ -1927,8 +1919,8 @@
       <c r="A64" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B64">
-        <v>19</v>
+      <c r="B64" t="str">
+        <v>Mathias Akampurira</v>
       </c>
       <c r="C64">
         <v>175000</v>
@@ -1941,8 +1933,8 @@
       <c r="A65" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B65">
-        <v>21</v>
+      <c r="B65" t="str">
+        <v>Simon Kulooba</v>
       </c>
       <c r="C65">
         <v>50000</v>
@@ -1955,8 +1947,8 @@
       <c r="A66" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B66">
-        <v>22</v>
+      <c r="B66" t="str">
+        <v>Frank Begumanya</v>
       </c>
       <c r="C66">
         <v>50000</v>
@@ -1969,8 +1961,8 @@
       <c r="A67" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B67">
-        <v>31</v>
+      <c r="B67" t="str">
+        <v>muzahura  alex</v>
       </c>
       <c r="C67">
         <v>150000</v>
@@ -1983,8 +1975,8 @@
       <c r="A68" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B68">
-        <v>24</v>
+      <c r="B68" t="str">
+        <v>kyomugasho jolly</v>
       </c>
       <c r="C68">
         <v>300000</v>
@@ -1997,8 +1989,8 @@
       <c r="A69" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B69">
-        <v>25</v>
+      <c r="B69" t="str">
+        <v>Madam director</v>
       </c>
       <c r="C69">
         <v>2000000</v>
@@ -2011,8 +2003,8 @@
       <c r="A70" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B70">
-        <v>2</v>
+      <c r="B70" t="str">
+        <v>Ariho Micheal</v>
       </c>
       <c r="C70">
         <v>50000</v>
@@ -2025,8 +2017,8 @@
       <c r="A71" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B71">
-        <v>3</v>
+      <c r="B71" t="str">
+        <v>Kyarisiima Justus</v>
       </c>
       <c r="C71">
         <v>100000</v>
@@ -2039,8 +2031,8 @@
       <c r="A72" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B72">
-        <v>5</v>
+      <c r="B72" t="str">
+        <v>Nayebare Prossy</v>
       </c>
       <c r="C72">
         <v>50000</v>
@@ -2053,8 +2045,8 @@
       <c r="A73" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B73">
-        <v>6</v>
+      <c r="B73" t="str">
+        <v>Sonia</v>
       </c>
       <c r="C73">
         <v>50000</v>
@@ -2067,8 +2059,8 @@
       <c r="A74" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B74">
-        <v>8</v>
+      <c r="B74" t="str">
+        <v>Mucunguzi Junior</v>
       </c>
       <c r="C74">
         <v>100000</v>
@@ -2081,8 +2073,8 @@
       <c r="A75" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B75">
-        <v>9</v>
+      <c r="B75" t="str">
+        <v>Ainembabazi Queen</v>
       </c>
       <c r="C75">
         <v>100000</v>
@@ -2095,8 +2087,8 @@
       <c r="A76" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B76">
-        <v>11</v>
+      <c r="B76" t="str">
+        <v>Ainebyona Mebo</v>
       </c>
       <c r="C76">
         <v>25000</v>
@@ -2109,8 +2101,8 @@
       <c r="A77" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B77">
-        <v>12</v>
+      <c r="B77" t="str">
+        <v>Mzee Fred Kakombe</v>
       </c>
       <c r="C77">
         <v>50000</v>
@@ -2123,8 +2115,8 @@
       <c r="A78" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B78">
-        <v>13</v>
+      <c r="B78" t="str">
+        <v>Jesica Kamuseveni</v>
       </c>
       <c r="C78">
         <v>50000</v>
@@ -2137,8 +2129,8 @@
       <c r="A79" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B79">
-        <v>14</v>
+      <c r="B79" t="str">
+        <v>Mathias Twijukye</v>
       </c>
       <c r="C79">
         <v>50000</v>
@@ -2151,8 +2143,8 @@
       <c r="A80" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B80">
-        <v>15</v>
+      <c r="B80" t="str">
+        <v>Nyangoma Sharon</v>
       </c>
       <c r="C80">
         <v>50000</v>
@@ -2165,8 +2157,8 @@
       <c r="A81" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B81">
-        <v>17</v>
+      <c r="B81" t="str">
+        <v>Nasasira Ainaea</v>
       </c>
       <c r="C81">
         <v>25000</v>
@@ -2179,8 +2171,8 @@
       <c r="A82" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B82">
-        <v>18</v>
+      <c r="B82" t="str">
+        <v>Nimusiima Sharon</v>
       </c>
       <c r="C82">
         <v>50000</v>
@@ -2193,8 +2185,8 @@
       <c r="A83" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B83">
-        <v>21</v>
+      <c r="B83" t="str">
+        <v>Simon Kulooba</v>
       </c>
       <c r="C83">
         <v>50000</v>
@@ -2207,8 +2199,8 @@
       <c r="A84" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B84">
-        <v>22</v>
+      <c r="B84" t="str">
+        <v>Frank Begumanya</v>
       </c>
       <c r="C84">
         <v>50000</v>
@@ -2221,8 +2213,8 @@
       <c r="A85" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B85">
-        <v>31</v>
+      <c r="B85" t="str">
+        <v>muzahura  alex</v>
       </c>
       <c r="C85">
         <v>150000</v>
@@ -2235,8 +2227,8 @@
       <c r="A86" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B86">
-        <v>24</v>
+      <c r="B86" t="str">
+        <v>kyomugasho jolly</v>
       </c>
       <c r="C86">
         <v>300000</v>
@@ -2249,8 +2241,8 @@
       <c r="A87" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B87">
-        <v>25</v>
+      <c r="B87" t="str">
+        <v>Madam director</v>
       </c>
       <c r="C87">
         <v>2000000</v>
@@ -2263,8 +2255,8 @@
       <c r="A88" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B88">
-        <v>34</v>
+      <c r="B88" t="str">
+        <v>Norman</v>
       </c>
       <c r="C88">
         <v>25000</v>
@@ -2277,8 +2269,8 @@
       <c r="A89" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B89">
-        <v>35</v>
+      <c r="B89" t="str">
+        <v>Elliot</v>
       </c>
       <c r="C89">
         <v>50000</v>
@@ -2291,8 +2283,8 @@
       <c r="A90" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B90">
-        <v>2</v>
+      <c r="B90" t="str">
+        <v>Ariho Micheal</v>
       </c>
       <c r="C90">
         <v>50000</v>
@@ -2305,8 +2297,8 @@
       <c r="A91" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B91">
-        <v>3</v>
+      <c r="B91" t="str">
+        <v>Kyarisiima Justus</v>
       </c>
       <c r="C91">
         <v>50000</v>
@@ -2319,8 +2311,8 @@
       <c r="A92" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B92">
-        <v>5</v>
+      <c r="B92" t="str">
+        <v>Nayebare Prossy</v>
       </c>
       <c r="C92">
         <v>50000</v>
@@ -2333,8 +2325,8 @@
       <c r="A93" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B93">
-        <v>6</v>
+      <c r="B93" t="str">
+        <v>Sonia</v>
       </c>
       <c r="C93">
         <v>50000</v>
@@ -2347,8 +2339,8 @@
       <c r="A94" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B94">
-        <v>7</v>
+      <c r="B94" t="str">
+        <v>Kazoora Francis</v>
       </c>
       <c r="C94">
         <v>50000</v>
@@ -2361,8 +2353,8 @@
       <c r="A95" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B95">
-        <v>8</v>
+      <c r="B95" t="str">
+        <v>Mucunguzi Junior</v>
       </c>
       <c r="C95">
         <v>75000</v>
@@ -2375,8 +2367,8 @@
       <c r="A96" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B96">
-        <v>9</v>
+      <c r="B96" t="str">
+        <v>Ainembabazi Queen</v>
       </c>
       <c r="C96">
         <v>100000</v>
@@ -2389,8 +2381,8 @@
       <c r="A97" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B97">
-        <v>10</v>
+      <c r="B97" t="str">
+        <v>Kanyesigye immaculate</v>
       </c>
       <c r="C97">
         <v>50000</v>
@@ -2403,8 +2395,8 @@
       <c r="A98" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B98">
-        <v>11</v>
+      <c r="B98" t="str">
+        <v>Ainebyona Mebo</v>
       </c>
       <c r="C98">
         <v>150000</v>
@@ -2417,8 +2409,8 @@
       <c r="A99" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B99">
-        <v>12</v>
+      <c r="B99" t="str">
+        <v>Mzee Fred Kakombe</v>
       </c>
       <c r="C99">
         <v>50000</v>
@@ -2431,8 +2423,8 @@
       <c r="A100" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B100">
-        <v>13</v>
+      <c r="B100" t="str">
+        <v>Jesica Kamuseveni</v>
       </c>
       <c r="C100">
         <v>50000</v>
@@ -2445,8 +2437,8 @@
       <c r="A101" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B101">
-        <v>14</v>
+      <c r="B101" t="str">
+        <v>Mathias Twijukye</v>
       </c>
       <c r="C101">
         <v>50000</v>
@@ -2459,8 +2451,8 @@
       <c r="A102" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B102">
-        <v>15</v>
+      <c r="B102" t="str">
+        <v>Nyangoma Sharon</v>
       </c>
       <c r="C102">
         <v>250000</v>
@@ -2473,8 +2465,8 @@
       <c r="A103" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B103">
-        <v>17</v>
+      <c r="B103" t="str">
+        <v>Nasasira Ainaea</v>
       </c>
       <c r="C103">
         <v>50000</v>
@@ -2487,8 +2479,8 @@
       <c r="A104" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B104">
-        <v>18</v>
+      <c r="B104" t="str">
+        <v>Nimusiima Sharon</v>
       </c>
       <c r="C104">
         <v>50000</v>
@@ -2501,8 +2493,8 @@
       <c r="A105" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B105">
-        <v>19</v>
+      <c r="B105" t="str">
+        <v>Mathias Akampurira</v>
       </c>
       <c r="C105">
         <v>175000</v>
@@ -2515,8 +2507,8 @@
       <c r="A106" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B106">
-        <v>20</v>
+      <c r="B106" t="str">
+        <v>Fednand Tumusiime</v>
       </c>
       <c r="C106">
         <v>50000</v>
@@ -2529,8 +2521,8 @@
       <c r="A107" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B107">
-        <v>21</v>
+      <c r="B107" t="str">
+        <v>Simon Kulooba</v>
       </c>
       <c r="C107">
         <v>50000</v>
@@ -2543,8 +2535,8 @@
       <c r="A108" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B108">
-        <v>22</v>
+      <c r="B108" t="str">
+        <v>Frank Begumanya</v>
       </c>
       <c r="C108">
         <v>50000</v>
@@ -2557,8 +2549,8 @@
       <c r="A109" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B109">
-        <v>31</v>
+      <c r="B109" t="str">
+        <v>muzahura  alex</v>
       </c>
       <c r="C109">
         <v>150000</v>
@@ -2571,8 +2563,8 @@
       <c r="A110" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B110">
-        <v>25</v>
+      <c r="B110" t="str">
+        <v>Madam director</v>
       </c>
       <c r="C110">
         <v>2000000</v>
@@ -2585,8 +2577,8 @@
       <c r="A111" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B111">
-        <v>34</v>
+      <c r="B111" t="str">
+        <v>Norman</v>
       </c>
       <c r="C111">
         <v>50000</v>
@@ -2599,8 +2591,8 @@
       <c r="A112" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B112">
-        <v>35</v>
+      <c r="B112" t="str">
+        <v>Elliot</v>
       </c>
       <c r="C112">
         <v>50000</v>
@@ -2613,8 +2605,8 @@
       <c r="A113" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B113">
-        <v>38</v>
+      <c r="B113" t="str">
+        <v>jolly</v>
       </c>
       <c r="C113">
         <v>300000</v>
@@ -2627,8 +2619,8 @@
       <c r="A114" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B114">
-        <v>37</v>
+      <c r="B114" t="str">
+        <v>Frank  manager</v>
       </c>
       <c r="C114">
         <v>50000</v>
@@ -2641,8 +2633,8 @@
       <c r="A115" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B115">
-        <v>2</v>
+      <c r="B115" t="str">
+        <v>Ariho Micheal</v>
       </c>
       <c r="C115">
         <v>50000</v>
@@ -2655,8 +2647,8 @@
       <c r="A116" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B116">
-        <v>3</v>
+      <c r="B116" t="str">
+        <v>Kyarisiima Justus</v>
       </c>
       <c r="C116">
         <v>100000</v>
@@ -2669,8 +2661,8 @@
       <c r="A117" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B117">
-        <v>5</v>
+      <c r="B117" t="str">
+        <v>Nayebare Prossy</v>
       </c>
       <c r="C117">
         <v>50000</v>
@@ -2683,8 +2675,8 @@
       <c r="A118" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B118">
-        <v>6</v>
+      <c r="B118" t="str">
+        <v>Sonia</v>
       </c>
       <c r="C118">
         <v>50000</v>
@@ -2697,8 +2689,8 @@
       <c r="A119" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B119">
-        <v>7</v>
+      <c r="B119" t="str">
+        <v>Kazoora Francis</v>
       </c>
       <c r="C119">
         <v>50000</v>
@@ -2711,8 +2703,8 @@
       <c r="A120" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B120">
-        <v>8</v>
+      <c r="B120" t="str">
+        <v>Mucunguzi Junior</v>
       </c>
       <c r="C120">
         <v>100000</v>
@@ -2725,8 +2717,8 @@
       <c r="A121" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B121">
-        <v>9</v>
+      <c r="B121" t="str">
+        <v>Ainembabazi Queen</v>
       </c>
       <c r="C121">
         <v>100000</v>
@@ -2739,8 +2731,8 @@
       <c r="A122" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B122">
-        <v>11</v>
+      <c r="B122" t="str">
+        <v>Ainebyona Mebo</v>
       </c>
       <c r="C122">
         <v>150000</v>
@@ -2753,8 +2745,8 @@
       <c r="A123" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B123">
-        <v>12</v>
+      <c r="B123" t="str">
+        <v>Mzee Fred Kakombe</v>
       </c>
       <c r="C123">
         <v>50000</v>
@@ -2767,8 +2759,8 @@
       <c r="A124" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B124">
-        <v>13</v>
+      <c r="B124" t="str">
+        <v>Jesica Kamuseveni</v>
       </c>
       <c r="C124">
         <v>50000</v>
@@ -2781,8 +2773,8 @@
       <c r="A125" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B125">
-        <v>14</v>
+      <c r="B125" t="str">
+        <v>Mathias Twijukye</v>
       </c>
       <c r="C125">
         <v>100000</v>
@@ -2795,8 +2787,8 @@
       <c r="A126" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B126">
-        <v>15</v>
+      <c r="B126" t="str">
+        <v>Nyangoma Sharon</v>
       </c>
       <c r="C126">
         <v>300000</v>
@@ -2809,8 +2801,8 @@
       <c r="A127" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B127">
-        <v>17</v>
+      <c r="B127" t="str">
+        <v>Nasasira Ainaea</v>
       </c>
       <c r="C127">
         <v>50000</v>
@@ -2823,8 +2815,8 @@
       <c r="A128" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B128">
-        <v>19</v>
+      <c r="B128" t="str">
+        <v>Mathias Akampurira</v>
       </c>
       <c r="C128">
         <v>175000</v>
@@ -2837,8 +2829,8 @@
       <c r="A129" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B129">
-        <v>20</v>
+      <c r="B129" t="str">
+        <v>Fednand Tumusiime</v>
       </c>
       <c r="C129">
         <v>50000</v>
@@ -2851,8 +2843,8 @@
       <c r="A130" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B130">
-        <v>21</v>
+      <c r="B130" t="str">
+        <v>Simon Kulooba</v>
       </c>
       <c r="C130">
         <v>50000</v>
@@ -2865,8 +2857,8 @@
       <c r="A131" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B131">
-        <v>22</v>
+      <c r="B131" t="str">
+        <v>Frank Begumanya</v>
       </c>
       <c r="C131">
         <v>50000</v>
@@ -2879,8 +2871,8 @@
       <c r="A132" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B132">
-        <v>31</v>
+      <c r="B132" t="str">
+        <v>muzahura  alex</v>
       </c>
       <c r="C132">
         <v>50000</v>
@@ -2893,8 +2885,8 @@
       <c r="A133" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B133">
-        <v>39</v>
+      <c r="B133" t="str">
+        <v>Amos</v>
       </c>
       <c r="C133">
         <v>150000</v>
@@ -2907,8 +2899,8 @@
       <c r="A134" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B134">
-        <v>25</v>
+      <c r="B134" t="str">
+        <v>Madam director</v>
       </c>
       <c r="C134">
         <v>2000000</v>
@@ -2921,8 +2913,8 @@
       <c r="A135" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B135">
-        <v>34</v>
+      <c r="B135" t="str">
+        <v>Norman</v>
       </c>
       <c r="C135">
         <v>50000</v>
@@ -2935,8 +2927,8 @@
       <c r="A136" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B136">
-        <v>35</v>
+      <c r="B136" t="str">
+        <v>Elliot</v>
       </c>
       <c r="C136">
         <v>50000</v>
@@ -2949,8 +2941,8 @@
       <c r="A137" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B137">
-        <v>38</v>
+      <c r="B137" t="str">
+        <v>jolly</v>
       </c>
       <c r="C137">
         <v>300000</v>
@@ -2963,8 +2955,8 @@
       <c r="A138" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B138">
-        <v>2</v>
+      <c r="B138" t="str">
+        <v>Ariho Micheal</v>
       </c>
       <c r="C138">
         <v>50000</v>
@@ -2977,8 +2969,8 @@
       <c r="A139" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B139">
-        <v>3</v>
+      <c r="B139" t="str">
+        <v>Kyarisiima Justus</v>
       </c>
       <c r="C139">
         <v>50000</v>
@@ -2991,8 +2983,8 @@
       <c r="A140" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B140">
-        <v>5</v>
+      <c r="B140" t="str">
+        <v>Nayebare Prossy</v>
       </c>
       <c r="C140">
         <v>50000</v>
@@ -3005,8 +2997,8 @@
       <c r="A141" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B141">
-        <v>7</v>
+      <c r="B141" t="str">
+        <v>Kazoora Francis</v>
       </c>
       <c r="C141">
         <v>50000</v>
@@ -3019,8 +3011,8 @@
       <c r="A142" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B142">
-        <v>9</v>
+      <c r="B142" t="str">
+        <v>Ainembabazi Queen</v>
       </c>
       <c r="C142">
         <v>100000</v>
@@ -3033,8 +3025,8 @@
       <c r="A143" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B143">
-        <v>10</v>
+      <c r="B143" t="str">
+        <v>Kanyesigye immaculate</v>
       </c>
       <c r="C143">
         <v>50000</v>
@@ -3047,8 +3039,8 @@
       <c r="A144" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B144">
-        <v>11</v>
+      <c r="B144" t="str">
+        <v>Ainebyona Mebo</v>
       </c>
       <c r="C144">
         <v>150000</v>
@@ -3061,8 +3053,8 @@
       <c r="A145" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B145">
-        <v>12</v>
+      <c r="B145" t="str">
+        <v>Mzee Fred Kakombe</v>
       </c>
       <c r="C145">
         <v>50000</v>
@@ -3075,8 +3067,8 @@
       <c r="A146" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B146">
-        <v>14</v>
+      <c r="B146" t="str">
+        <v>Mathias Twijukye</v>
       </c>
       <c r="C146">
         <v>80000</v>
@@ -3089,8 +3081,8 @@
       <c r="A147" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B147">
-        <v>15</v>
+      <c r="B147" t="str">
+        <v>Nyangoma Sharon</v>
       </c>
       <c r="C147">
         <v>300000</v>
@@ -3103,8 +3095,8 @@
       <c r="A148" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B148">
-        <v>17</v>
+      <c r="B148" t="str">
+        <v>Nasasira Ainaea</v>
       </c>
       <c r="C148">
         <v>50000</v>
@@ -3117,8 +3109,8 @@
       <c r="A149" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B149">
-        <v>18</v>
+      <c r="B149" t="str">
+        <v>Nimusiima Sharon</v>
       </c>
       <c r="C149">
         <v>50000</v>
@@ -3131,8 +3123,8 @@
       <c r="A150" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B150">
-        <v>19</v>
+      <c r="B150" t="str">
+        <v>Mathias Akampurira</v>
       </c>
       <c r="C150">
         <v>175000</v>
@@ -3145,8 +3137,8 @@
       <c r="A151" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B151">
-        <v>20</v>
+      <c r="B151" t="str">
+        <v>Fednand Tumusiime</v>
       </c>
       <c r="C151">
         <v>75000</v>
@@ -3159,8 +3151,8 @@
       <c r="A152" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B152">
-        <v>21</v>
+      <c r="B152" t="str">
+        <v>Simon Kulooba</v>
       </c>
       <c r="C152">
         <v>50000</v>
@@ -3173,8 +3165,8 @@
       <c r="A153" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B153">
-        <v>22</v>
+      <c r="B153" t="str">
+        <v>Frank Begumanya</v>
       </c>
       <c r="C153">
         <v>50000</v>
@@ -3187,8 +3179,8 @@
       <c r="A154" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B154">
-        <v>31</v>
+      <c r="B154" t="str">
+        <v>muzahura  alex</v>
       </c>
       <c r="C154">
         <v>100000</v>
@@ -3201,8 +3193,8 @@
       <c r="A155" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B155">
-        <v>39</v>
+      <c r="B155" t="str">
+        <v>Amos</v>
       </c>
       <c r="C155">
         <v>100000</v>
@@ -3215,8 +3207,8 @@
       <c r="A156" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B156">
-        <v>25</v>
+      <c r="B156" t="str">
+        <v>Madam director</v>
       </c>
       <c r="C156">
         <v>2000000</v>
@@ -3229,8 +3221,8 @@
       <c r="A157" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B157">
-        <v>34</v>
+      <c r="B157" t="str">
+        <v>Norman</v>
       </c>
       <c r="C157">
         <v>50000</v>
@@ -3243,8 +3235,8 @@
       <c r="A158" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B158">
-        <v>35</v>
+      <c r="B158" t="str">
+        <v>Elliot</v>
       </c>
       <c r="C158">
         <v>50000</v>
@@ -3257,8 +3249,8 @@
       <c r="A159" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B159">
-        <v>38</v>
+      <c r="B159" t="str">
+        <v>jolly</v>
       </c>
       <c r="C159">
         <v>300000</v>
@@ -3271,8 +3263,8 @@
       <c r="A160" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B160">
-        <v>37</v>
+      <c r="B160" t="str">
+        <v>Frank  manager</v>
       </c>
       <c r="C160">
         <v>100000</v>
@@ -3297,7 +3289,7 @@
         <v>Loan_ID</v>
       </c>
       <c r="B1" t="str">
-        <v>Member_ID</v>
+        <v>Member</v>
       </c>
       <c r="C1" t="str">
         <v>Principal_UGX</v>
@@ -3316,8 +3308,8 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
+      <c r="B2" t="str">
+        <v>Ariho Micheal</v>
       </c>
       <c r="C2">
         <v>500000</v>
@@ -3336,8 +3328,8 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
+      <c r="B3" t="str">
+        <v>Kyarisiima Justus</v>
       </c>
       <c r="C3">
         <v>300000</v>
@@ -3356,8 +3348,8 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>4</v>
+      <c r="B4" t="str">
+        <v>Kasumbuza Cosmas</v>
       </c>
       <c r="C4">
         <v>150000</v>
@@ -3376,8 +3368,8 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>6</v>
+      <c r="B5" t="str">
+        <v>Sonia</v>
       </c>
       <c r="C5">
         <v>400000</v>
@@ -3396,8 +3388,8 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>7</v>
+      <c r="B6" t="str">
+        <v>Kazoora Francis</v>
       </c>
       <c r="C6">
         <v>350000</v>
@@ -3409,15 +3401,15 @@
         <v>2026-01-31</v>
       </c>
       <c r="F6" t="str">
-        <v>Active</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>8</v>
+      <c r="B7" t="str">
+        <v>Mucunguzi Junior</v>
       </c>
       <c r="C7">
         <v>160000</v>
@@ -3429,15 +3421,15 @@
         <v>2026-01-31</v>
       </c>
       <c r="F7" t="str">
-        <v>Active</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>9</v>
+      <c r="B8" t="str">
+        <v>Ainembabazi Queen</v>
       </c>
       <c r="C8">
         <v>200000</v>
@@ -3449,15 +3441,15 @@
         <v>2026-01-31</v>
       </c>
       <c r="F8" t="str">
-        <v>Active</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>10</v>
+      <c r="B9" t="str">
+        <v>Kanyesigye immaculate</v>
       </c>
       <c r="C9">
         <v>500000</v>
@@ -3476,8 +3468,8 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>12</v>
+      <c r="B10" t="str">
+        <v>Mzee Fred Kakombe</v>
       </c>
       <c r="C10">
         <v>235000</v>
@@ -3496,8 +3488,8 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
-        <v>13</v>
+      <c r="B11" t="str">
+        <v>Jesica Kamuseveni</v>
       </c>
       <c r="C11">
         <v>400000</v>
@@ -3516,8 +3508,8 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
-        <v>14</v>
+      <c r="B12" t="str">
+        <v>Mathias Twijukye</v>
       </c>
       <c r="C12">
         <v>130000</v>
@@ -3529,15 +3521,15 @@
         <v>2026-01-31</v>
       </c>
       <c r="F12" t="str">
-        <v>Active</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
-        <v>16</v>
+      <c r="B13" t="str">
+        <v>Rwihura Duncan</v>
       </c>
       <c r="C13">
         <v>700000</v>
@@ -3549,15 +3541,15 @@
         <v>2026-01-31</v>
       </c>
       <c r="F13" t="str">
-        <v>Active</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>17</v>
+      <c r="B14" t="str">
+        <v>Nasasira Ainaea</v>
       </c>
       <c r="C14">
         <v>600000</v>
@@ -3569,15 +3561,15 @@
         <v>2026-01-31</v>
       </c>
       <c r="F14" t="str">
-        <v>Active</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15">
-        <v>18</v>
+      <c r="B15" t="str">
+        <v>Nimusiima Sharon</v>
       </c>
       <c r="C15">
         <v>200000</v>
@@ -3589,15 +3581,15 @@
         <v>2026-01-31</v>
       </c>
       <c r="F15" t="str">
-        <v>Active</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16">
-        <v>20</v>
+      <c r="B16" t="str">
+        <v>Fednand Tumusiime</v>
       </c>
       <c r="C16">
         <v>150000</v>
@@ -3609,15 +3601,15 @@
         <v>2026-01-31</v>
       </c>
       <c r="F16" t="str">
-        <v>Active</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17">
-        <v>21</v>
+      <c r="B17" t="str">
+        <v>Simon Kulooba</v>
       </c>
       <c r="C17">
         <v>400000</v>
@@ -3636,8 +3628,8 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18">
-        <v>22</v>
+      <c r="B18" t="str">
+        <v>Frank Begumanya</v>
       </c>
       <c r="C18">
         <v>250000</v>
@@ -3656,8 +3648,8 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19">
-        <v>23</v>
+      <c r="B19" t="str">
+        <v>Alex Muzahura</v>
       </c>
       <c r="C19">
         <v>70000</v>
@@ -3676,8 +3668,8 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20">
-        <v>11</v>
+      <c r="B20" t="str">
+        <v>Ainebyona Mebo</v>
       </c>
       <c r="C20">
         <v>100000</v>
@@ -3689,15 +3681,15 @@
         <v>2026-02-28</v>
       </c>
       <c r="F20" t="str">
-        <v>Active</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>31</v>
+      <c r="B21" t="str">
+        <v>muzahura  alex</v>
       </c>
       <c r="C21">
         <v>90000</v>
@@ -3716,8 +3708,8 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22">
-        <v>24</v>
+      <c r="B22" t="str">
+        <v>kyomugasho jolly</v>
       </c>
       <c r="C22">
         <v>400000</v>
@@ -3736,8 +3728,8 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23">
-        <v>19</v>
+      <c r="B23" t="str">
+        <v>Mathias Akampurira</v>
       </c>
       <c r="C23">
         <v>160000</v>
@@ -3749,15 +3741,15 @@
         <v>2026-04-30</v>
       </c>
       <c r="F23" t="str">
-        <v>Active</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24">
-        <v>37</v>
+      <c r="B24" t="str">
+        <v>Frank  manager</v>
       </c>
       <c r="C24">
         <v>507000</v>
@@ -3769,15 +3761,15 @@
         <v>2026-04-30</v>
       </c>
       <c r="F24" t="str">
-        <v>Active</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25">
-        <v>35</v>
+      <c r="B25" t="str">
+        <v>Elliot</v>
       </c>
       <c r="C25">
         <v>300000</v>
@@ -3796,8 +3788,8 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26">
-        <v>5</v>
+      <c r="B26" t="str">
+        <v>Nayebare Prossy</v>
       </c>
       <c r="C26">
         <v>500000</v>
@@ -3816,8 +3808,8 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27">
-        <v>34</v>
+      <c r="B27" t="str">
+        <v>Norman</v>
       </c>
       <c r="C27">
         <v>250000</v>
@@ -3836,8 +3828,8 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28">
-        <v>38</v>
+      <c r="B28" t="str">
+        <v>jolly</v>
       </c>
       <c r="C28">
         <v>300000</v>
@@ -3861,19 +3853,22 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:E82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Date</v>
       </c>
       <c r="B1" t="str">
+        <v>Member</v>
+      </c>
+      <c r="C1" t="str">
         <v>Loan_ID</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Amount_UGX</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -3881,13 +3876,16 @@
       <c r="A2" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
+        <v>Ariho Micheal</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>50000</v>
-      </c>
-      <c r="D2" t="str">
+      <c r="D2">
+        <v>50000</v>
+      </c>
+      <c r="E2" t="str">
         <v>Payroll Repayment - 2026-01</v>
       </c>
     </row>
@@ -3895,13 +3893,16 @@
       <c r="A3" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
+        <v>Kyarisiima Justus</v>
+      </c>
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>20000</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>Payroll Repayment - 2026-01</v>
       </c>
     </row>
@@ -3909,13 +3910,16 @@
       <c r="A4" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="str">
+        <v>Kazoora Francis</v>
+      </c>
+      <c r="C4">
         <v>5</v>
       </c>
-      <c r="C4">
-        <v>50000</v>
-      </c>
-      <c r="D4" t="str">
+      <c r="D4">
+        <v>50000</v>
+      </c>
+      <c r="E4" t="str">
         <v>Payroll Repayment - 2026-01</v>
       </c>
     </row>
@@ -3923,13 +3927,16 @@
       <c r="A5" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="str">
+        <v>Mucunguzi Junior</v>
+      </c>
+      <c r="C5">
         <v>6</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>30000</v>
       </c>
-      <c r="D5" t="str">
+      <c r="E5" t="str">
         <v>Payroll Repayment - 2026-01</v>
       </c>
     </row>
@@ -3937,13 +3944,16 @@
       <c r="A6" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="str">
+        <v>Ainembabazi Queen</v>
+      </c>
+      <c r="C6">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>20000</v>
       </c>
-      <c r="D6" t="str">
+      <c r="E6" t="str">
         <v>Payroll Repayment - 2026-01</v>
       </c>
     </row>
@@ -3951,13 +3961,16 @@
       <c r="A7" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="str">
+        <v>Jesica Kamuseveni</v>
+      </c>
+      <c r="C7">
         <v>10</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>100000</v>
       </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <v>Payroll Repayment - 2026-01</v>
       </c>
     </row>
@@ -3965,13 +3978,16 @@
       <c r="A8" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="str">
+        <v>Mathias Twijukye</v>
+      </c>
+      <c r="C8">
         <v>11</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>80000</v>
       </c>
-      <c r="D8" t="str">
+      <c r="E8" t="str">
         <v>Payroll Repayment - 2026-01</v>
       </c>
     </row>
@@ -3979,13 +3995,16 @@
       <c r="A9" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="str">
+        <v>Rwihura Duncan</v>
+      </c>
+      <c r="C9">
         <v>12</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>100000</v>
       </c>
-      <c r="D9" t="str">
+      <c r="E9" t="str">
         <v>Payroll Repayment - 2026-01</v>
       </c>
     </row>
@@ -3993,13 +4012,16 @@
       <c r="A10" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="str">
+        <v>Nasasira Ainaea</v>
+      </c>
+      <c r="C10">
         <v>13</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>100000</v>
       </c>
-      <c r="D10" t="str">
+      <c r="E10" t="str">
         <v>Payroll Repayment - 2026-01</v>
       </c>
     </row>
@@ -4007,13 +4029,16 @@
       <c r="A11" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="str">
+        <v>Ariho Micheal</v>
+      </c>
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>40000</v>
       </c>
-      <c r="D11" t="str">
+      <c r="E11" t="str">
         <v>Payroll Repayment - 2026-02</v>
       </c>
     </row>
@@ -4021,13 +4046,16 @@
       <c r="A12" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="str">
+        <v>Kazoora Francis</v>
+      </c>
+      <c r="C12">
         <v>5</v>
       </c>
-      <c r="C12">
-        <v>50000</v>
-      </c>
-      <c r="D12" t="str">
+      <c r="D12">
+        <v>50000</v>
+      </c>
+      <c r="E12" t="str">
         <v>Payroll Repayment - 2026-02</v>
       </c>
     </row>
@@ -4035,13 +4063,16 @@
       <c r="A13" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="str">
+        <v>Mzee Fred Kakombe</v>
+      </c>
+      <c r="C13">
         <v>9</v>
       </c>
-      <c r="C13">
-        <v>50000</v>
-      </c>
-      <c r="D13" t="str">
+      <c r="D13">
+        <v>50000</v>
+      </c>
+      <c r="E13" t="str">
         <v>Payroll Repayment - 2026-02</v>
       </c>
     </row>
@@ -4049,13 +4080,16 @@
       <c r="A14" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="str">
+        <v>Jesica Kamuseveni</v>
+      </c>
+      <c r="C14">
         <v>10</v>
       </c>
-      <c r="C14">
-        <v>50000</v>
-      </c>
-      <c r="D14" t="str">
+      <c r="D14">
+        <v>50000</v>
+      </c>
+      <c r="E14" t="str">
         <v>Payroll Repayment - 2026-02</v>
       </c>
     </row>
@@ -4063,13 +4097,16 @@
       <c r="A15" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="str">
+        <v>Rwihura Duncan</v>
+      </c>
+      <c r="C15">
         <v>12</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>100000</v>
       </c>
-      <c r="D15" t="str">
+      <c r="E15" t="str">
         <v>Payroll Repayment - 2026-02</v>
       </c>
     </row>
@@ -4077,13 +4114,16 @@
       <c r="A16" t="str">
         <v>2026-02-28</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="str">
+        <v>Nasasira Ainaea</v>
+      </c>
+      <c r="C16">
         <v>13</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>171000</v>
       </c>
-      <c r="D16" t="str">
+      <c r="E16" t="str">
         <v>Payroll Repayment - 2026-02</v>
       </c>
     </row>
@@ -4091,13 +4131,16 @@
       <c r="A17" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="str">
+        <v>Ariho Micheal</v>
+      </c>
+      <c r="C17">
         <v>1</v>
       </c>
-      <c r="C17">
-        <v>50000</v>
-      </c>
-      <c r="D17" t="str">
+      <c r="D17">
+        <v>50000</v>
+      </c>
+      <c r="E17" t="str">
         <v>Payroll Repayment - 2026-03</v>
       </c>
     </row>
@@ -4105,13 +4148,16 @@
       <c r="A18" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="str">
+        <v>Kazoora Francis</v>
+      </c>
+      <c r="C18">
         <v>5</v>
       </c>
-      <c r="C18">
-        <v>50000</v>
-      </c>
-      <c r="D18" t="str">
+      <c r="D18">
+        <v>50000</v>
+      </c>
+      <c r="E18" t="str">
         <v>Payroll Repayment - 2026-03</v>
       </c>
     </row>
@@ -4119,13 +4165,16 @@
       <c r="A19" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="str">
+        <v>Mucunguzi Junior</v>
+      </c>
+      <c r="C19">
         <v>6</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>30000</v>
       </c>
-      <c r="D19" t="str">
+      <c r="E19" t="str">
         <v>Payroll Repayment - 2026-03</v>
       </c>
     </row>
@@ -4133,13 +4182,16 @@
       <c r="A20" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="str">
+        <v>Kanyesigye immaculate</v>
+      </c>
+      <c r="C20">
         <v>8</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>100000</v>
       </c>
-      <c r="D20" t="str">
+      <c r="E20" t="str">
         <v>Payroll Repayment - 2026-03</v>
       </c>
     </row>
@@ -4147,13 +4199,16 @@
       <c r="A21" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="str">
+        <v>Mathias Twijukye</v>
+      </c>
+      <c r="C21">
         <v>11</v>
       </c>
-      <c r="C21">
-        <v>50000</v>
-      </c>
-      <c r="D21" t="str">
+      <c r="D21">
+        <v>50000</v>
+      </c>
+      <c r="E21" t="str">
         <v>Payroll Repayment - 2026-03</v>
       </c>
     </row>
@@ -4161,13 +4216,16 @@
       <c r="A22" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="str">
+        <v>Rwihura Duncan</v>
+      </c>
+      <c r="C22">
         <v>12</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>327400</v>
       </c>
-      <c r="D22" t="str">
+      <c r="E22" t="str">
         <v>Payroll Repayment - 2026-03</v>
       </c>
     </row>
@@ -4175,13 +4233,16 @@
       <c r="A23" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="str">
+        <v>Nasasira Ainaea</v>
+      </c>
+      <c r="C23">
         <v>13</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>152100</v>
       </c>
-      <c r="D23" t="str">
+      <c r="E23" t="str">
         <v>Payroll Repayment - 2026-03</v>
       </c>
     </row>
@@ -4189,13 +4250,16 @@
       <c r="A24" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="str">
+        <v>Nimusiima Sharon</v>
+      </c>
+      <c r="C24">
         <v>14</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>80000</v>
       </c>
-      <c r="D24" t="str">
+      <c r="E24" t="str">
         <v>Payroll Repayment - 2026-03</v>
       </c>
     </row>
@@ -4203,13 +4267,16 @@
       <c r="A25" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="str">
+        <v>Fednand Tumusiime</v>
+      </c>
+      <c r="C25">
         <v>15</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>70000</v>
       </c>
-      <c r="D25" t="str">
+      <c r="E25" t="str">
         <v>Payroll Repayment - 2026-03</v>
       </c>
     </row>
@@ -4217,13 +4284,16 @@
       <c r="A26" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="str">
+        <v>Ariho Micheal</v>
+      </c>
+      <c r="C26">
         <v>1</v>
       </c>
-      <c r="C26">
-        <v>50000</v>
-      </c>
-      <c r="D26" t="str">
+      <c r="D26">
+        <v>50000</v>
+      </c>
+      <c r="E26" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4231,13 +4301,16 @@
       <c r="A27" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="str">
+        <v>Kyarisiima Justus</v>
+      </c>
+      <c r="C27">
         <v>2</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>20000</v>
       </c>
-      <c r="D27" t="str">
+      <c r="E27" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4245,13 +4318,16 @@
       <c r="A28" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="str">
+        <v>Kazoora Francis</v>
+      </c>
+      <c r="C28">
         <v>5</v>
       </c>
-      <c r="C28">
-        <v>50000</v>
-      </c>
-      <c r="D28" t="str">
+      <c r="D28">
+        <v>50000</v>
+      </c>
+      <c r="E28" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4259,13 +4335,16 @@
       <c r="A29" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="str">
+        <v>Mucunguzi Junior</v>
+      </c>
+      <c r="C29">
         <v>6</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>10000</v>
       </c>
-      <c r="D29" t="str">
+      <c r="E29" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4273,13 +4352,16 @@
       <c r="A30" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="str">
+        <v>Ainembabazi Queen</v>
+      </c>
+      <c r="C30">
         <v>7</v>
       </c>
-      <c r="C30">
-        <v>50000</v>
-      </c>
-      <c r="D30" t="str">
+      <c r="D30">
+        <v>50000</v>
+      </c>
+      <c r="E30" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4287,13 +4369,16 @@
       <c r="A31" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="str">
+        <v>Kanyesigye immaculate</v>
+      </c>
+      <c r="C31">
         <v>8</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>130000</v>
       </c>
-      <c r="D31" t="str">
+      <c r="E31" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4301,13 +4386,16 @@
       <c r="A32" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="str">
+        <v>Ainebyona Mebo</v>
+      </c>
+      <c r="C32">
         <v>19</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>100000</v>
       </c>
-      <c r="D32" t="str">
+      <c r="E32" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4315,13 +4403,16 @@
       <c r="A33" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="str">
+        <v>Jesica Kamuseveni</v>
+      </c>
+      <c r="C33">
         <v>10</v>
       </c>
-      <c r="C33">
-        <v>50000</v>
-      </c>
-      <c r="D33" t="str">
+      <c r="D33">
+        <v>50000</v>
+      </c>
+      <c r="E33" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4329,13 +4420,16 @@
       <c r="A34" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="str">
+        <v>Rwihura Duncan</v>
+      </c>
+      <c r="C34">
         <v>12</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>295000</v>
       </c>
-      <c r="D34" t="str">
+      <c r="E34" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4343,13 +4437,16 @@
       <c r="A35" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="str">
+        <v>Nasasira Ainaea</v>
+      </c>
+      <c r="C35">
         <v>13</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>100000</v>
       </c>
-      <c r="D35" t="str">
+      <c r="E35" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4357,13 +4454,16 @@
       <c r="A36" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="str">
+        <v>Nimusiima Sharon</v>
+      </c>
+      <c r="C36">
         <v>14</v>
       </c>
-      <c r="C36">
-        <v>50000</v>
-      </c>
-      <c r="D36" t="str">
+      <c r="D36">
+        <v>50000</v>
+      </c>
+      <c r="E36" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4371,13 +4471,16 @@
       <c r="A37" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="str">
+        <v>Mathias Akampurira</v>
+      </c>
+      <c r="C37">
         <v>22</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>160000</v>
       </c>
-      <c r="D37" t="str">
+      <c r="E37" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4385,13 +4488,16 @@
       <c r="A38" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B38">
+      <c r="B38" t="str">
+        <v>Fednand Tumusiime</v>
+      </c>
+      <c r="C38">
         <v>15</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>100000</v>
       </c>
-      <c r="D38" t="str">
+      <c r="E38" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4399,13 +4505,16 @@
       <c r="A39" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="B39">
+      <c r="B39" t="str">
+        <v>Frank  manager</v>
+      </c>
+      <c r="C39">
         <v>23</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>507000</v>
       </c>
-      <c r="D39" t="str">
+      <c r="E39" t="str">
         <v>Payroll Repayment - 2026-04</v>
       </c>
     </row>
@@ -4413,13 +4522,16 @@
       <c r="A40" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B40">
+      <c r="B40" t="str">
+        <v>Ariho Micheal</v>
+      </c>
+      <c r="C40">
         <v>1</v>
       </c>
-      <c r="C40">
-        <v>50000</v>
-      </c>
-      <c r="D40" t="str">
+      <c r="D40">
+        <v>50000</v>
+      </c>
+      <c r="E40" t="str">
         <v>Payroll Repayment - 2026-05</v>
       </c>
     </row>
@@ -4427,13 +4539,16 @@
       <c r="A41" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B41">
+      <c r="B41" t="str">
+        <v>Kazoora Francis</v>
+      </c>
+      <c r="C41">
         <v>5</v>
       </c>
-      <c r="C41">
-        <v>50000</v>
-      </c>
-      <c r="D41" t="str">
+      <c r="D41">
+        <v>50000</v>
+      </c>
+      <c r="E41" t="str">
         <v>Payroll Repayment - 2026-05</v>
       </c>
     </row>
@@ -4441,13 +4556,16 @@
       <c r="A42" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B42">
+      <c r="B42" t="str">
+        <v>Mucunguzi Junior</v>
+      </c>
+      <c r="C42">
         <v>6</v>
       </c>
-      <c r="C42">
-        <v>50000</v>
-      </c>
-      <c r="D42" t="str">
+      <c r="D42">
+        <v>50000</v>
+      </c>
+      <c r="E42" t="str">
         <v>Payroll Repayment - 2026-05</v>
       </c>
     </row>
@@ -4455,13 +4573,16 @@
       <c r="A43" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B43">
+      <c r="B43" t="str">
+        <v>Ainembabazi Queen</v>
+      </c>
+      <c r="C43">
         <v>7</v>
       </c>
-      <c r="C43">
-        <v>50000</v>
-      </c>
-      <c r="D43" t="str">
+      <c r="D43">
+        <v>50000</v>
+      </c>
+      <c r="E43" t="str">
         <v>Payroll Repayment - 2026-05</v>
       </c>
     </row>
@@ -4469,13 +4590,16 @@
       <c r="A44" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B44">
+      <c r="B44" t="str">
+        <v>Kanyesigye immaculate</v>
+      </c>
+      <c r="C44">
         <v>8</v>
       </c>
-      <c r="C44">
-        <v>50000</v>
-      </c>
-      <c r="D44" t="str">
+      <c r="D44">
+        <v>50000</v>
+      </c>
+      <c r="E44" t="str">
         <v>Payroll Repayment - 2026-05</v>
       </c>
     </row>
@@ -4483,13 +4607,16 @@
       <c r="A45" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B45">
+      <c r="B45" t="str">
+        <v>Mzee Fred Kakombe</v>
+      </c>
+      <c r="C45">
         <v>9</v>
       </c>
-      <c r="C45">
-        <v>50000</v>
-      </c>
-      <c r="D45" t="str">
+      <c r="D45">
+        <v>50000</v>
+      </c>
+      <c r="E45" t="str">
         <v>Payroll Repayment - 2026-05</v>
       </c>
     </row>
@@ -4497,13 +4624,16 @@
       <c r="A46" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B46">
+      <c r="B46" t="str">
+        <v>Jesica Kamuseveni</v>
+      </c>
+      <c r="C46">
         <v>10</v>
       </c>
-      <c r="C46">
-        <v>50000</v>
-      </c>
-      <c r="D46" t="str">
+      <c r="D46">
+        <v>50000</v>
+      </c>
+      <c r="E46" t="str">
         <v>Payroll Repayment - 2026-05</v>
       </c>
     </row>
@@ -4511,13 +4641,16 @@
       <c r="A47" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B47">
+      <c r="B47" t="str">
+        <v>Mathias Twijukye</v>
+      </c>
+      <c r="C47">
         <v>11</v>
       </c>
-      <c r="C47">
-        <v>50000</v>
-      </c>
-      <c r="D47" t="str">
+      <c r="D47">
+        <v>50000</v>
+      </c>
+      <c r="E47" t="str">
         <v>Payroll Repayment - 2026-05</v>
       </c>
     </row>
@@ -4525,13 +4658,16 @@
       <c r="A48" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B48">
+      <c r="B48" t="str">
+        <v>Rwihura Duncan</v>
+      </c>
+      <c r="C48">
         <v>12</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>200000</v>
       </c>
-      <c r="D48" t="str">
+      <c r="E48" t="str">
         <v>Payroll Repayment - 2026-05</v>
       </c>
     </row>
@@ -4539,13 +4675,16 @@
       <c r="A49" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B49">
+      <c r="B49" t="str">
+        <v>Nasasira Ainaea</v>
+      </c>
+      <c r="C49">
         <v>13</v>
       </c>
-      <c r="C49">
-        <v>50000</v>
-      </c>
-      <c r="D49" t="str">
+      <c r="D49">
+        <v>50000</v>
+      </c>
+      <c r="E49" t="str">
         <v>Payroll Repayment - 2026-05</v>
       </c>
     </row>
@@ -4553,13 +4692,16 @@
       <c r="A50" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B50">
+      <c r="B50" t="str">
+        <v>Nimusiima Sharon</v>
+      </c>
+      <c r="C50">
         <v>14</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>20000</v>
       </c>
-      <c r="D50" t="str">
+      <c r="E50" t="str">
         <v>Payroll Repayment - 2026-05</v>
       </c>
     </row>
@@ -4567,13 +4709,16 @@
       <c r="A51" t="str">
         <v>2026-05-31</v>
       </c>
-      <c r="B51">
+      <c r="B51" t="str">
+        <v>Fednand Tumusiime</v>
+      </c>
+      <c r="C51">
         <v>15</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>60000</v>
       </c>
-      <c r="D51" t="str">
+      <c r="E51" t="str">
         <v>Payroll Repayment - 2026-05</v>
       </c>
     </row>
@@ -4581,13 +4726,16 @@
       <c r="A52" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B52">
+      <c r="B52" t="str">
+        <v>Ariho Micheal</v>
+      </c>
+      <c r="C52">
         <v>1</v>
       </c>
-      <c r="C52">
-        <v>50000</v>
-      </c>
-      <c r="D52" t="str">
+      <c r="D52">
+        <v>50000</v>
+      </c>
+      <c r="E52" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4595,13 +4743,16 @@
       <c r="A53" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B53">
+      <c r="B53" t="str">
+        <v>Kyarisiima Justus</v>
+      </c>
+      <c r="C53">
         <v>2</v>
       </c>
-      <c r="C53">
-        <v>50000</v>
-      </c>
-      <c r="D53" t="str">
+      <c r="D53">
+        <v>50000</v>
+      </c>
+      <c r="E53" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4609,13 +4760,16 @@
       <c r="A54" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B54">
+      <c r="B54" t="str">
+        <v>Nayebare Prossy</v>
+      </c>
+      <c r="C54">
         <v>25</v>
       </c>
-      <c r="C54">
-        <v>50000</v>
-      </c>
-      <c r="D54" t="str">
+      <c r="D54">
+        <v>50000</v>
+      </c>
+      <c r="E54" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4623,13 +4777,16 @@
       <c r="A55" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B55">
+      <c r="B55" t="str">
+        <v>Kazoora Francis</v>
+      </c>
+      <c r="C55">
         <v>5</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>80000</v>
       </c>
-      <c r="D55" t="str">
+      <c r="E55" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4637,13 +4794,16 @@
       <c r="A56" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B56">
+      <c r="B56" t="str">
+        <v>Mucunguzi Junior</v>
+      </c>
+      <c r="C56">
         <v>6</v>
       </c>
-      <c r="C56">
+      <c r="D56">
         <v>45000</v>
       </c>
-      <c r="D56" t="str">
+      <c r="E56" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4651,13 +4811,16 @@
       <c r="A57" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B57">
+      <c r="B57" t="str">
+        <v>Ainembabazi Queen</v>
+      </c>
+      <c r="C57">
         <v>7</v>
       </c>
-      <c r="C57">
-        <v>50000</v>
-      </c>
-      <c r="D57" t="str">
+      <c r="D57">
+        <v>50000</v>
+      </c>
+      <c r="E57" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4665,13 +4828,16 @@
       <c r="A58" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B58">
+      <c r="B58" t="str">
+        <v>Kanyesigye immaculate</v>
+      </c>
+      <c r="C58">
         <v>8</v>
       </c>
-      <c r="C58">
+      <c r="D58">
         <v>150000</v>
       </c>
-      <c r="D58" t="str">
+      <c r="E58" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4679,13 +4845,16 @@
       <c r="A59" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B59">
+      <c r="B59" t="str">
+        <v>Mzee Fred Kakombe</v>
+      </c>
+      <c r="C59">
         <v>9</v>
       </c>
-      <c r="C59">
-        <v>50000</v>
-      </c>
-      <c r="D59" t="str">
+      <c r="D59">
+        <v>50000</v>
+      </c>
+      <c r="E59" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4693,13 +4862,16 @@
       <c r="A60" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B60">
+      <c r="B60" t="str">
+        <v>Jesica Kamuseveni</v>
+      </c>
+      <c r="C60">
         <v>10</v>
       </c>
-      <c r="C60">
-        <v>50000</v>
-      </c>
-      <c r="D60" t="str">
+      <c r="D60">
+        <v>50000</v>
+      </c>
+      <c r="E60" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4707,13 +4879,16 @@
       <c r="A61" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B61">
+      <c r="B61" t="str">
+        <v>Mathias Twijukye</v>
+      </c>
+      <c r="C61">
         <v>11</v>
       </c>
-      <c r="C61">
-        <v>50000</v>
-      </c>
-      <c r="D61" t="str">
+      <c r="D61">
+        <v>50000</v>
+      </c>
+      <c r="E61" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4721,13 +4896,16 @@
       <c r="A62" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B62">
+      <c r="B62" t="str">
+        <v>Nasasira Ainaea</v>
+      </c>
+      <c r="C62">
         <v>13</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>200000</v>
       </c>
-      <c r="D62" t="str">
+      <c r="E62" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4735,13 +4913,16 @@
       <c r="A63" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B63">
+      <c r="B63" t="str">
+        <v>Nimusiima Sharon</v>
+      </c>
+      <c r="C63">
         <v>14</v>
       </c>
-      <c r="C63">
-        <v>50000</v>
-      </c>
-      <c r="D63" t="str">
+      <c r="D63">
+        <v>50000</v>
+      </c>
+      <c r="E63" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4749,13 +4930,16 @@
       <c r="A64" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B64">
+      <c r="B64" t="str">
+        <v>Fednand Tumusiime</v>
+      </c>
+      <c r="C64">
         <v>15</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <v>80000</v>
       </c>
-      <c r="D64" t="str">
+      <c r="E64" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4763,13 +4947,16 @@
       <c r="A65" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B65">
+      <c r="B65" t="str">
+        <v>Simon Kulooba</v>
+      </c>
+      <c r="C65">
         <v>16</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <v>30000</v>
       </c>
-      <c r="D65" t="str">
+      <c r="E65" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4777,13 +4964,16 @@
       <c r="A66" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B66">
+      <c r="B66" t="str">
+        <v>Frank Begumanya</v>
+      </c>
+      <c r="C66">
         <v>17</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>30000</v>
       </c>
-      <c r="D66" t="str">
+      <c r="E66" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4791,13 +4981,16 @@
       <c r="A67" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B67">
+      <c r="B67" t="str">
+        <v>muzahura  alex</v>
+      </c>
+      <c r="C67">
         <v>20</v>
       </c>
-      <c r="C67">
-        <v>50000</v>
-      </c>
-      <c r="D67" t="str">
+      <c r="D67">
+        <v>50000</v>
+      </c>
+      <c r="E67" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4805,13 +4998,16 @@
       <c r="A68" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B68">
+      <c r="B68" t="str">
+        <v>Norman</v>
+      </c>
+      <c r="C68">
         <v>26</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>20000</v>
       </c>
-      <c r="D68" t="str">
+      <c r="E68" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4819,13 +5015,16 @@
       <c r="A69" t="str">
         <v>2026-06-30</v>
       </c>
-      <c r="B69">
+      <c r="B69" t="str">
+        <v>Frank  manager</v>
+      </c>
+      <c r="C69">
         <v>23</v>
       </c>
-      <c r="C69">
+      <c r="D69">
         <v>500000</v>
       </c>
-      <c r="D69" t="str">
+      <c r="E69" t="str">
         <v>Payroll Repayment - 2026-06</v>
       </c>
     </row>
@@ -4833,13 +5032,16 @@
       <c r="A70" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B70">
+      <c r="B70" t="str">
+        <v>Ariho Micheal</v>
+      </c>
+      <c r="C70">
         <v>1</v>
       </c>
-      <c r="C70">
-        <v>50000</v>
-      </c>
-      <c r="D70" t="str">
+      <c r="D70">
+        <v>50000</v>
+      </c>
+      <c r="E70" t="str">
         <v>Payroll Repayment - 2026-07</v>
       </c>
     </row>
@@ -4847,13 +5049,16 @@
       <c r="A71" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B71">
+      <c r="B71" t="str">
+        <v>Nayebare Prossy</v>
+      </c>
+      <c r="C71">
         <v>25</v>
       </c>
-      <c r="C71">
-        <v>50000</v>
-      </c>
-      <c r="D71" t="str">
+      <c r="D71">
+        <v>50000</v>
+      </c>
+      <c r="E71" t="str">
         <v>Payroll Repayment - 2026-07</v>
       </c>
     </row>
@@ -4861,13 +5066,16 @@
       <c r="A72" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B72">
+      <c r="B72" t="str">
+        <v>Sonia</v>
+      </c>
+      <c r="C72">
         <v>4</v>
       </c>
-      <c r="C72">
+      <c r="D72">
         <v>200000</v>
       </c>
-      <c r="D72" t="str">
+      <c r="E72" t="str">
         <v>Payroll Repayment - 2026-07</v>
       </c>
     </row>
@@ -4875,13 +5083,16 @@
       <c r="A73" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B73">
+      <c r="B73" t="str">
+        <v>Kazoora Francis</v>
+      </c>
+      <c r="C73">
         <v>5</v>
       </c>
-      <c r="C73">
-        <v>50000</v>
-      </c>
-      <c r="D73" t="str">
+      <c r="D73">
+        <v>50000</v>
+      </c>
+      <c r="E73" t="str">
         <v>Payroll Repayment - 2026-07</v>
       </c>
     </row>
@@ -4889,13 +5100,16 @@
       <c r="A74" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B74">
+      <c r="B74" t="str">
+        <v>Mucunguzi Junior</v>
+      </c>
+      <c r="C74">
         <v>6</v>
       </c>
-      <c r="C74">
+      <c r="D74">
         <v>100000</v>
       </c>
-      <c r="D74" t="str">
+      <c r="E74" t="str">
         <v>Payroll Repayment - 2026-07</v>
       </c>
     </row>
@@ -4903,13 +5117,16 @@
       <c r="A75" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B75">
+      <c r="B75" t="str">
+        <v>Ainembabazi Queen</v>
+      </c>
+      <c r="C75">
         <v>7</v>
       </c>
-      <c r="C75">
+      <c r="D75">
         <v>80000</v>
       </c>
-      <c r="D75" t="str">
+      <c r="E75" t="str">
         <v>Payroll Repayment - 2026-07</v>
       </c>
     </row>
@@ -4917,13 +5134,16 @@
       <c r="A76" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B76">
+      <c r="B76" t="str">
+        <v>Mathias Twijukye</v>
+      </c>
+      <c r="C76">
         <v>11</v>
       </c>
-      <c r="C76">
-        <v>50000</v>
-      </c>
-      <c r="D76" t="str">
+      <c r="D76">
+        <v>50000</v>
+      </c>
+      <c r="E76" t="str">
         <v>Payroll Repayment - 2026-07</v>
       </c>
     </row>
@@ -4931,13 +5151,16 @@
       <c r="A77" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B77">
+      <c r="B77" t="str">
+        <v>Nasasira Ainaea</v>
+      </c>
+      <c r="C77">
         <v>13</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>150000</v>
       </c>
-      <c r="D77" t="str">
+      <c r="E77" t="str">
         <v>Payroll Repayment - 2026-07</v>
       </c>
     </row>
@@ -4945,13 +5168,16 @@
       <c r="A78" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B78">
+      <c r="B78" t="str">
+        <v>Nimusiima Sharon</v>
+      </c>
+      <c r="C78">
         <v>14</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>30000</v>
       </c>
-      <c r="D78" t="str">
+      <c r="E78" t="str">
         <v>Payroll Repayment - 2026-07</v>
       </c>
     </row>
@@ -4959,13 +5185,16 @@
       <c r="A79" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B79">
+      <c r="B79" t="str">
+        <v>Fednand Tumusiime</v>
+      </c>
+      <c r="C79">
         <v>15</v>
       </c>
-      <c r="C79">
-        <v>50000</v>
-      </c>
-      <c r="D79" t="str">
+      <c r="D79">
+        <v>50000</v>
+      </c>
+      <c r="E79" t="str">
         <v>Payroll Repayment - 2026-07</v>
       </c>
     </row>
@@ -4973,13 +5202,16 @@
       <c r="A80" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B80">
+      <c r="B80" t="str">
+        <v>Simon Kulooba</v>
+      </c>
+      <c r="C80">
         <v>16</v>
       </c>
-      <c r="C80">
+      <c r="D80">
         <v>80000</v>
       </c>
-      <c r="D80" t="str">
+      <c r="E80" t="str">
         <v>Payroll Repayment - 2026-07</v>
       </c>
     </row>
@@ -4987,13 +5219,16 @@
       <c r="A81" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B81">
+      <c r="B81" t="str">
+        <v>Frank Begumanya</v>
+      </c>
+      <c r="C81">
         <v>17</v>
       </c>
-      <c r="C81">
+      <c r="D81">
         <v>30000</v>
       </c>
-      <c r="D81" t="str">
+      <c r="E81" t="str">
         <v>Payroll Repayment - 2026-07</v>
       </c>
     </row>
@@ -5001,19 +5236,22 @@
       <c r="A82" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="B82">
+      <c r="B82" t="str">
+        <v>Norman</v>
+      </c>
+      <c r="C82">
         <v>26</v>
       </c>
-      <c r="C82">
+      <c r="D82">
         <v>30000</v>
       </c>
-      <c r="D82" t="str">
+      <c r="E82" t="str">
         <v>Payroll Repayment - 2026-07</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E82"/>
   </ignoredErrors>
 </worksheet>
 </file>